--- a/data/pipeline/generation_and_energy_storage_connection_pipeline.xlsx
+++ b/data/pipeline/generation_and_energy_storage_connection_pipeline.xlsx
@@ -6,12 +6,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\holbrookr\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://transpowernz.sharepoint.com/sites/cm010/Queue Management/Project management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC80EA69-69E1-4D86-9E36-CC6CCC5271FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{A77AF943-CE17-4F36-9520-8369D3909623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5D3CD63-37FF-4F57-9A3A-65AD880D4386}"/>
   <bookViews>
-    <workbookView xWindow="10068" yWindow="12888" windowWidth="23256" windowHeight="13896" xr2:uid="{98A1789F-FB35-4A96-AF00-70C1209832A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{98A1789F-FB35-4A96-AF00-70C1209832A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Forward Pipeline" sheetId="1" r:id="rId1"/>
@@ -2710,6 +2710,9 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2718,9 +2721,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -3137,29 +3137,29 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AC157"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.109375" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
     <col min="3" max="3" width="39" customWidth="1"/>
-    <col min="4" max="4" width="49.109375" customWidth="1"/>
+    <col min="4" max="4" width="49.140625" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.5546875" customWidth="1"/>
-    <col min="13" max="13" width="31.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" customWidth="1"/>
+    <col min="13" max="13" width="31.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="27" style="1" customWidth="1"/>
-    <col min="15" max="15" width="26.44140625" customWidth="1"/>
-    <col min="16" max="16" width="5.33203125" customWidth="1"/>
-    <col min="17" max="17" width="35.88671875" customWidth="1"/>
-    <col min="18" max="18" width="165.88671875" customWidth="1"/>
+    <col min="15" max="15" width="26.42578125" customWidth="1"/>
+    <col min="16" max="16" width="5.28515625" customWidth="1"/>
+    <col min="17" max="17" width="35.85546875" customWidth="1"/>
+    <col min="18" max="18" width="165.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
@@ -3214,7 +3214,7 @@
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
     </row>
-    <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="88" t="s">
         <v>16</v>
       </c>
@@ -3269,7 +3269,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="88" t="s">
         <v>27</v>
       </c>
@@ -3324,7 +3324,7 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
     </row>
-    <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="138" t="s">
         <v>37</v>
       </c>
@@ -3361,8 +3361,8 @@
       <c r="L4" s="108">
         <v>0.87</v>
       </c>
-      <c r="M4" s="136" t="s">
-        <v>34</v>
+      <c r="M4" s="69" t="s">
+        <v>449</v>
       </c>
       <c r="N4" s="136" t="s">
         <v>35</v>
@@ -3379,7 +3379,7 @@
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
     </row>
-    <row r="5" spans="1:21" s="72" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" s="72" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="132" t="s">
         <v>43</v>
       </c>
@@ -3434,7 +3434,7 @@
       <c r="T5" s="74"/>
       <c r="U5" s="74"/>
     </row>
-    <row r="6" spans="1:21" s="72" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" s="72" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="92" t="s">
         <v>49</v>
       </c>
@@ -3487,7 +3487,7 @@
       <c r="T6" s="74"/>
       <c r="U6" s="74"/>
     </row>
-    <row r="7" spans="1:21" s="72" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" s="72" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="88">
         <v>38476</v>
       </c>
@@ -3540,7 +3540,7 @@
       <c r="T7" s="74"/>
       <c r="U7" s="74"/>
     </row>
-    <row r="8" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="88" t="s">
         <v>59</v>
       </c>
@@ -3593,7 +3593,7 @@
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="88" t="s">
         <v>65</v>
       </c>
@@ -3646,7 +3646,7 @@
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="88" t="s">
         <v>69</v>
       </c>
@@ -3699,7 +3699,7 @@
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="88" t="s">
         <v>74</v>
       </c>
@@ -3752,7 +3752,7 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="88" t="s">
         <v>79</v>
       </c>
@@ -3805,7 +3805,7 @@
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="88" t="s">
         <v>81</v>
       </c>
@@ -3858,7 +3858,7 @@
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="88" t="s">
         <v>86</v>
       </c>
@@ -3911,7 +3911,7 @@
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="88" t="s">
         <v>87</v>
       </c>
@@ -3964,7 +3964,7 @@
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="88" t="s">
         <v>92</v>
       </c>
@@ -4017,7 +4017,7 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="88" t="s">
         <v>95</v>
       </c>
@@ -4070,7 +4070,7 @@
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="99" t="s">
         <v>97</v>
       </c>
@@ -4123,7 +4123,7 @@
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="88" t="s">
         <v>100</v>
       </c>
@@ -4176,7 +4176,7 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="88" t="s">
         <v>102</v>
       </c>
@@ -4229,7 +4229,7 @@
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="88" t="s">
         <v>106</v>
       </c>
@@ -4282,7 +4282,7 @@
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="88" t="s">
         <v>108</v>
       </c>
@@ -4334,7 +4334,7 @@
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="88" t="s">
         <v>109</v>
       </c>
@@ -4387,7 +4387,7 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="88">
         <v>37580</v>
       </c>
@@ -4439,7 +4439,7 @@
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="88" t="s">
         <v>117</v>
       </c>
@@ -4492,7 +4492,7 @@
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="88" t="s">
         <v>122</v>
       </c>
@@ -4545,7 +4545,7 @@
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="32"/>
       <c r="B27" s="32"/>
       <c r="C27" s="32"/>
@@ -4568,7 +4568,7 @@
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
     </row>
-    <row r="28" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
         <v>0</v>
       </c>
@@ -4617,7 +4617,7 @@
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="110" t="s">
         <v>131</v>
       </c>
@@ -4666,7 +4666,7 @@
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="110" t="s">
         <v>146</v>
       </c>
@@ -4715,7 +4715,7 @@
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
     </row>
-    <row r="31" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="117" t="s">
         <v>148</v>
       </c>
@@ -4764,7 +4764,7 @@
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="117" t="s">
         <v>125</v>
       </c>
@@ -4813,7 +4813,7 @@
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="110" t="s">
         <v>209</v>
       </c>
@@ -4862,7 +4862,7 @@
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="110" t="s">
         <v>133</v>
       </c>
@@ -4911,7 +4911,7 @@
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="110" t="s">
         <v>149</v>
       </c>
@@ -4960,7 +4960,7 @@
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="110" t="s">
         <v>151</v>
       </c>
@@ -5009,7 +5009,7 @@
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="117" t="s">
         <v>171</v>
       </c>
@@ -5058,7 +5058,7 @@
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="110" t="s">
         <v>173</v>
       </c>
@@ -5107,7 +5107,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="110" t="s">
         <v>140</v>
       </c>
@@ -5156,7 +5156,7 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="110" t="s">
         <v>142</v>
       </c>
@@ -5205,7 +5205,7 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="117" t="s">
         <v>161</v>
       </c>
@@ -5254,7 +5254,7 @@
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="110">
         <v>37586</v>
       </c>
@@ -5303,7 +5303,7 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="110" t="s">
         <v>136</v>
       </c>
@@ -5352,7 +5352,7 @@
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
     </row>
-    <row r="44" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="110">
         <v>37588</v>
       </c>
@@ -5401,7 +5401,7 @@
       <c r="T44" s="3"/>
       <c r="U44" s="4"/>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="110">
         <v>38058</v>
       </c>
@@ -5450,7 +5450,7 @@
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="110" t="s">
         <v>170</v>
       </c>
@@ -5499,7 +5499,7 @@
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
     </row>
-    <row r="47" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="110" t="s">
         <v>219</v>
       </c>
@@ -5548,7 +5548,7 @@
       <c r="T47" s="3"/>
       <c r="U47" s="4"/>
     </row>
-    <row r="48" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="110" t="s">
         <v>152</v>
       </c>
@@ -5597,7 +5597,7 @@
       <c r="T48" s="3"/>
       <c r="U48" s="4"/>
     </row>
-    <row r="49" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="117" t="s">
         <v>155</v>
       </c>
@@ -5646,7 +5646,7 @@
       <c r="T49" s="3"/>
       <c r="U49" s="4"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="110" t="s">
         <v>176</v>
       </c>
@@ -5695,7 +5695,7 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
     </row>
-    <row r="51" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="110" t="s">
         <v>166</v>
       </c>
@@ -5744,7 +5744,7 @@
       <c r="T51" s="3"/>
       <c r="U51" s="4"/>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="110" t="s">
         <v>143</v>
       </c>
@@ -5793,7 +5793,7 @@
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="110" t="s">
         <v>145</v>
       </c>
@@ -5842,7 +5842,7 @@
       <c r="T53" s="3"/>
       <c r="U53" s="3"/>
     </row>
-    <row r="54" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="110" t="s">
         <v>174</v>
       </c>
@@ -5891,7 +5891,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="4"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="110" t="s">
         <v>181</v>
       </c>
@@ -5940,7 +5940,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
     </row>
-    <row r="56" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="110" t="s">
         <v>199</v>
       </c>
@@ -5989,7 +5989,7 @@
       <c r="T56" s="3"/>
       <c r="U56" s="4"/>
     </row>
-    <row r="57" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="110" t="s">
         <v>213</v>
       </c>
@@ -6038,7 +6038,7 @@
       <c r="T57" s="3"/>
       <c r="U57" s="4"/>
     </row>
-    <row r="58" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="110" t="s">
         <v>214</v>
       </c>
@@ -6087,7 +6087,7 @@
       <c r="T58" s="3"/>
       <c r="U58" s="4"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="117" t="s">
         <v>164</v>
       </c>
@@ -6136,7 +6136,7 @@
       <c r="T59" s="3"/>
       <c r="U59" s="3"/>
     </row>
-    <row r="60" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="110" t="s">
         <v>179</v>
       </c>
@@ -6185,7 +6185,7 @@
       <c r="T60" s="3"/>
       <c r="U60" s="3"/>
     </row>
-    <row r="61" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="110" t="s">
         <v>159</v>
       </c>
@@ -6234,7 +6234,7 @@
       <c r="T61" s="3"/>
       <c r="U61" s="3"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="110">
         <v>37645</v>
       </c>
@@ -6283,7 +6283,7 @@
       <c r="T62" s="3"/>
       <c r="U62" s="3"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="110">
         <v>37696</v>
       </c>
@@ -6332,7 +6332,7 @@
       <c r="T63" s="3"/>
       <c r="U63" s="3"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="110" t="s">
         <v>216</v>
       </c>
@@ -6381,7 +6381,7 @@
       <c r="T64" s="3"/>
       <c r="U64" s="3"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="110" t="s">
         <v>168</v>
       </c>
@@ -6430,7 +6430,7 @@
       <c r="T65" s="3"/>
       <c r="U65" s="3"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="110" t="s">
         <v>203</v>
       </c>
@@ -6479,7 +6479,7 @@
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="110" t="s">
         <v>205</v>
       </c>
@@ -6528,7 +6528,7 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="110" t="s">
         <v>207</v>
       </c>
@@ -6577,7 +6577,7 @@
       <c r="T68" s="3"/>
       <c r="U68" s="3"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="110" t="s">
         <v>183</v>
       </c>
@@ -6626,7 +6626,7 @@
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="110" t="s">
         <v>156</v>
       </c>
@@ -6675,7 +6675,7 @@
       <c r="T70" s="3"/>
       <c r="U70" s="3"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="110" t="s">
         <v>158</v>
       </c>
@@ -6724,7 +6724,7 @@
       <c r="T71" s="3"/>
       <c r="U71" s="3"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="110" t="s">
         <v>190</v>
       </c>
@@ -6773,7 +6773,7 @@
       <c r="T72" s="3"/>
       <c r="U72" s="3"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="110" t="s">
         <v>212</v>
       </c>
@@ -6822,7 +6822,7 @@
       <c r="T73" s="3"/>
       <c r="U73" s="3"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="110" t="s">
         <v>178</v>
       </c>
@@ -6871,7 +6871,7 @@
       <c r="T74" s="3"/>
       <c r="U74" s="3"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="110" t="s">
         <v>201</v>
       </c>
@@ -6920,7 +6920,7 @@
       <c r="T75" s="3"/>
       <c r="U75" s="3"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="110" t="s">
         <v>206</v>
       </c>
@@ -6969,7 +6969,7 @@
       <c r="T76" s="3"/>
       <c r="U76" s="3"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="110" t="s">
         <v>186</v>
       </c>
@@ -7018,7 +7018,7 @@
       <c r="T77" s="3"/>
       <c r="U77" s="3"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="110" t="s">
         <v>192</v>
       </c>
@@ -7067,7 +7067,7 @@
       <c r="T78" s="3"/>
       <c r="U78" s="3"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="110" t="s">
         <v>194</v>
       </c>
@@ -7116,7 +7116,7 @@
       <c r="T79" s="3"/>
       <c r="U79" s="3"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="157" t="s">
         <v>195</v>
       </c>
@@ -7165,7 +7165,7 @@
       <c r="T80" s="3"/>
       <c r="U80" s="3"/>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="88" t="s">
         <v>197</v>
       </c>
@@ -7214,7 +7214,7 @@
       <c r="T81" s="3"/>
       <c r="U81" s="3"/>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="57"/>
       <c r="B82" s="57"/>
       <c r="C82" s="32"/>
@@ -7237,7 +7237,7 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
     </row>
-    <row r="83" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="29" t="s">
         <v>0</v>
       </c>
@@ -7284,7 +7284,7 @@
       <c r="T83" s="3"/>
       <c r="U83" s="3"/>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="91" t="s">
         <v>221</v>
       </c>
@@ -7331,7 +7331,7 @@
       <c r="T84" s="3"/>
       <c r="U84" s="3"/>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="91" t="s">
         <v>224</v>
       </c>
@@ -7378,7 +7378,7 @@
       <c r="T85" s="3"/>
       <c r="U85" s="3"/>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="91" t="s">
         <v>226</v>
       </c>
@@ -7425,7 +7425,7 @@
       <c r="T86" s="3"/>
       <c r="U86" s="3"/>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="91" t="s">
         <v>227</v>
       </c>
@@ -7472,7 +7472,7 @@
       <c r="T87" s="3"/>
       <c r="U87" s="3"/>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="91" t="s">
         <v>229</v>
       </c>
@@ -7519,7 +7519,7 @@
       <c r="T88" s="3"/>
       <c r="U88" s="3"/>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="91" t="s">
         <v>231</v>
       </c>
@@ -7566,7 +7566,7 @@
       <c r="T89" s="3"/>
       <c r="U89" s="3"/>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="91" t="s">
         <v>232</v>
       </c>
@@ -7613,7 +7613,7 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
     </row>
-    <row r="91" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="91" t="s">
         <v>233</v>
       </c>
@@ -7660,7 +7660,7 @@
       <c r="T91" s="3"/>
       <c r="U91" s="3"/>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="91" t="s">
         <v>235</v>
       </c>
@@ -7707,7 +7707,7 @@
       <c r="T92" s="3"/>
       <c r="U92" s="3"/>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="91" t="s">
         <v>236</v>
       </c>
@@ -7754,7 +7754,7 @@
       <c r="T93" s="3"/>
       <c r="U93" s="3"/>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="91" t="s">
         <v>239</v>
       </c>
@@ -7801,7 +7801,7 @@
       <c r="T94" s="3"/>
       <c r="U94" s="3"/>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="91" t="s">
         <v>240</v>
       </c>
@@ -7848,7 +7848,7 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="91" t="s">
         <v>241</v>
       </c>
@@ -7895,7 +7895,7 @@
       <c r="T96" s="3"/>
       <c r="U96" s="3"/>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="91" t="s">
         <v>243</v>
       </c>
@@ -7942,7 +7942,7 @@
       <c r="T97" s="3"/>
       <c r="U97" s="3"/>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="91" t="s">
         <v>244</v>
       </c>
@@ -7989,7 +7989,7 @@
       <c r="T98" s="3"/>
       <c r="U98" s="3"/>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="91" t="s">
         <v>246</v>
       </c>
@@ -8036,7 +8036,7 @@
       <c r="T99" s="3"/>
       <c r="U99" s="3"/>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="124" t="s">
         <v>248</v>
       </c>
@@ -8083,7 +8083,7 @@
       <c r="T100" s="3"/>
       <c r="U100" s="3"/>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="13"/>
@@ -8104,7 +8104,7 @@
       <c r="T101" s="3"/>
       <c r="U101" s="3"/>
     </row>
-    <row r="102" spans="1:21" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:21" ht="32.25" x14ac:dyDescent="0.25">
       <c r="A102" s="29" t="s">
         <v>0</v>
       </c>
@@ -8153,7 +8153,7 @@
       <c r="T102" s="3"/>
       <c r="U102" s="3"/>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="139" t="s">
         <v>252</v>
       </c>
@@ -8202,7 +8202,7 @@
       <c r="T103" s="3"/>
       <c r="U103" s="3"/>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="139" t="s">
         <v>257</v>
       </c>
@@ -8251,7 +8251,7 @@
       <c r="T104" s="3"/>
       <c r="U104" s="3"/>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="139" t="s">
         <v>258</v>
       </c>
@@ -8300,7 +8300,7 @@
       <c r="T105" s="3"/>
       <c r="U105" s="3"/>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="139" t="s">
         <v>260</v>
       </c>
@@ -8349,7 +8349,7 @@
       <c r="T106" s="3"/>
       <c r="U106" s="3"/>
     </row>
-    <row r="107" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="139" t="s">
         <v>262</v>
       </c>
@@ -8397,7 +8397,7 @@
       <c r="S107" s="3"/>
       <c r="T107" s="3"/>
     </row>
-    <row r="108" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="139" t="s">
         <v>264</v>
       </c>
@@ -8445,7 +8445,7 @@
       <c r="S108" s="3"/>
       <c r="T108" s="3"/>
     </row>
-    <row r="109" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="139" t="s">
         <v>265</v>
       </c>
@@ -8491,7 +8491,7 @@
       <c r="S109" s="3"/>
       <c r="T109" s="3"/>
     </row>
-    <row r="110" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="139" t="s">
         <v>267</v>
       </c>
@@ -8539,7 +8539,7 @@
       <c r="S110" s="3"/>
       <c r="T110" s="3"/>
     </row>
-    <row r="111" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="139" t="s">
         <v>269</v>
       </c>
@@ -8585,7 +8585,7 @@
       <c r="S111" s="3"/>
       <c r="T111" s="3"/>
     </row>
-    <row r="112" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="139" t="s">
         <v>271</v>
       </c>
@@ -8633,7 +8633,7 @@
       <c r="S112" s="3"/>
       <c r="T112" s="3"/>
     </row>
-    <row r="113" spans="1:29" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:29" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="139" t="s">
         <v>273</v>
       </c>
@@ -8681,7 +8681,7 @@
       <c r="S113" s="3"/>
       <c r="T113" s="3"/>
     </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A114" s="139" t="s">
         <v>275</v>
       </c>
@@ -8727,7 +8727,7 @@
       <c r="S114" s="3"/>
       <c r="T114" s="3"/>
     </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A115" s="139" t="s">
         <v>276</v>
       </c>
@@ -8773,7 +8773,7 @@
       <c r="S115" s="3"/>
       <c r="T115" s="3"/>
     </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A116" s="139" t="s">
         <v>277</v>
       </c>
@@ -8819,7 +8819,7 @@
       <c r="S116" s="3"/>
       <c r="T116" s="3"/>
     </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A117" s="139" t="s">
         <v>278</v>
       </c>
@@ -8865,7 +8865,7 @@
       <c r="S117" s="3"/>
       <c r="T117" s="3"/>
     </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A118" s="139" t="s">
         <v>279</v>
       </c>
@@ -8911,7 +8911,7 @@
       <c r="S118" s="3"/>
       <c r="T118" s="3"/>
     </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A119" s="139" t="s">
         <v>280</v>
       </c>
@@ -8957,7 +8957,7 @@
       <c r="S119" s="3"/>
       <c r="T119" s="3"/>
     </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A120" s="139" t="s">
         <v>282</v>
       </c>
@@ -9003,7 +9003,7 @@
       <c r="S120" s="3"/>
       <c r="T120" s="3"/>
     </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A121" s="139" t="s">
         <v>283</v>
       </c>
@@ -9049,7 +9049,7 @@
       <c r="S121" s="3"/>
       <c r="T121" s="3"/>
     </row>
-    <row r="122" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A122" s="139" t="s">
         <v>284</v>
       </c>
@@ -9095,7 +9095,7 @@
       <c r="S122" s="3"/>
       <c r="T122" s="3"/>
     </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A123" s="139" t="s">
         <v>286</v>
       </c>
@@ -9143,7 +9143,7 @@
       <c r="S123" s="3"/>
       <c r="T123" s="3"/>
     </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A124" s="139" t="s">
         <v>288</v>
       </c>
@@ -9189,7 +9189,7 @@
       <c r="S124" s="3"/>
       <c r="T124" s="3"/>
     </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A125" s="139" t="s">
         <v>290</v>
       </c>
@@ -9235,7 +9235,7 @@
       <c r="S125" s="3"/>
       <c r="T125" s="3"/>
     </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A126" s="139" t="s">
         <v>292</v>
       </c>
@@ -9281,7 +9281,7 @@
       <c r="S126" s="3"/>
       <c r="T126" s="3"/>
     </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A127" s="139" t="s">
         <v>293</v>
       </c>
@@ -9327,7 +9327,7 @@
       <c r="S127" s="3"/>
       <c r="T127" s="3"/>
     </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A128" s="139" t="s">
         <v>295</v>
       </c>
@@ -9375,7 +9375,7 @@
       <c r="U128" s="70"/>
       <c r="AC128" s="70"/>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="139" t="s">
         <v>296</v>
       </c>
@@ -9421,7 +9421,7 @@
       <c r="S129" s="3"/>
       <c r="T129" s="3"/>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="139" t="s">
         <v>297</v>
       </c>
@@ -9467,7 +9467,7 @@
       <c r="S130" s="3"/>
       <c r="T130" s="3"/>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="139" t="s">
         <v>299</v>
       </c>
@@ -9513,7 +9513,7 @@
       <c r="S131" s="3"/>
       <c r="T131" s="3"/>
     </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="139" t="s">
         <v>301</v>
       </c>
@@ -9559,7 +9559,7 @@
       <c r="S132" s="3"/>
       <c r="T132" s="3"/>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="139" t="s">
         <v>303</v>
       </c>
@@ -9605,7 +9605,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="139" t="s">
         <v>305</v>
       </c>
@@ -9651,7 +9651,7 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
     </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="139" t="s">
         <v>306</v>
       </c>
@@ -9697,7 +9697,7 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
     </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="139" t="s">
         <v>308</v>
       </c>
@@ -9743,7 +9743,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
     </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="152" t="s">
         <v>310</v>
       </c>
@@ -9789,7 +9789,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
     </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="152" t="s">
         <v>313</v>
       </c>
@@ -9835,7 +9835,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
     </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="68"/>
       <c r="B139" s="68"/>
       <c r="C139" s="3"/>
@@ -9857,7 +9857,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
     </row>
-    <row r="140" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="6" t="s">
@@ -9882,24 +9882,24 @@
       <c r="T140" s="3"/>
       <c r="U140" s="3"/>
     </row>
-    <row r="141" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
-      <c r="C141" s="176" t="s">
+      <c r="C141" s="177" t="s">
         <v>315</v>
       </c>
-      <c r="D141" s="176"/>
-      <c r="E141" s="176"/>
-      <c r="F141" s="176"/>
-      <c r="G141" s="176"/>
-      <c r="H141" s="176"/>
-      <c r="I141" s="176"/>
-      <c r="J141" s="176"/>
-      <c r="K141" s="176"/>
-      <c r="L141" s="176"/>
-      <c r="M141" s="176"/>
-      <c r="N141" s="176"/>
-      <c r="O141" s="176"/>
+      <c r="D141" s="177"/>
+      <c r="E141" s="177"/>
+      <c r="F141" s="177"/>
+      <c r="G141" s="177"/>
+      <c r="H141" s="177"/>
+      <c r="I141" s="177"/>
+      <c r="J141" s="177"/>
+      <c r="K141" s="177"/>
+      <c r="L141" s="177"/>
+      <c r="M141" s="177"/>
+      <c r="N141" s="177"/>
+      <c r="O141" s="177"/>
       <c r="P141" s="3"/>
       <c r="Q141" s="3"/>
       <c r="R141" s="3"/>
@@ -9907,24 +9907,24 @@
       <c r="T141" s="3"/>
       <c r="U141" s="3"/>
     </row>
-    <row r="142" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
-      <c r="C142" s="177" t="s">
+      <c r="C142" s="178" t="s">
         <v>316</v>
       </c>
-      <c r="D142" s="177"/>
-      <c r="E142" s="177"/>
-      <c r="F142" s="177"/>
-      <c r="G142" s="177"/>
-      <c r="H142" s="177"/>
-      <c r="I142" s="177"/>
-      <c r="J142" s="177"/>
-      <c r="K142" s="177"/>
-      <c r="L142" s="177"/>
-      <c r="M142" s="177"/>
-      <c r="N142" s="177"/>
-      <c r="O142" s="177"/>
+      <c r="D142" s="178"/>
+      <c r="E142" s="178"/>
+      <c r="F142" s="178"/>
+      <c r="G142" s="178"/>
+      <c r="H142" s="178"/>
+      <c r="I142" s="178"/>
+      <c r="J142" s="178"/>
+      <c r="K142" s="178"/>
+      <c r="L142" s="178"/>
+      <c r="M142" s="178"/>
+      <c r="N142" s="178"/>
+      <c r="O142" s="178"/>
       <c r="P142" s="3"/>
       <c r="Q142" s="3"/>
       <c r="R142" s="3"/>
@@ -9932,24 +9932,24 @@
       <c r="T142" s="3"/>
       <c r="U142" s="3"/>
     </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
-      <c r="C143" s="177" t="s">
+      <c r="C143" s="178" t="s">
         <v>317</v>
       </c>
-      <c r="D143" s="177"/>
-      <c r="E143" s="177"/>
-      <c r="F143" s="177"/>
-      <c r="G143" s="177"/>
-      <c r="H143" s="177"/>
-      <c r="I143" s="177"/>
-      <c r="J143" s="177"/>
-      <c r="K143" s="177"/>
-      <c r="L143" s="177"/>
-      <c r="M143" s="177"/>
-      <c r="N143" s="177"/>
-      <c r="O143" s="177"/>
+      <c r="D143" s="178"/>
+      <c r="E143" s="178"/>
+      <c r="F143" s="178"/>
+      <c r="G143" s="178"/>
+      <c r="H143" s="178"/>
+      <c r="I143" s="178"/>
+      <c r="J143" s="178"/>
+      <c r="K143" s="178"/>
+      <c r="L143" s="178"/>
+      <c r="M143" s="178"/>
+      <c r="N143" s="178"/>
+      <c r="O143" s="178"/>
       <c r="P143" s="3"/>
       <c r="Q143" s="3"/>
       <c r="R143" s="3"/>
@@ -9957,24 +9957,24 @@
       <c r="T143" s="3"/>
       <c r="U143" s="3"/>
     </row>
-    <row r="144" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
-      <c r="C144" s="177" t="s">
+      <c r="C144" s="178" t="s">
         <v>318</v>
       </c>
-      <c r="D144" s="177"/>
-      <c r="E144" s="177"/>
-      <c r="F144" s="177"/>
-      <c r="G144" s="177"/>
-      <c r="H144" s="177"/>
-      <c r="I144" s="177"/>
-      <c r="J144" s="177"/>
-      <c r="K144" s="177"/>
-      <c r="L144" s="177"/>
-      <c r="M144" s="177"/>
-      <c r="N144" s="177"/>
-      <c r="O144" s="177"/>
+      <c r="D144" s="178"/>
+      <c r="E144" s="178"/>
+      <c r="F144" s="178"/>
+      <c r="G144" s="178"/>
+      <c r="H144" s="178"/>
+      <c r="I144" s="178"/>
+      <c r="J144" s="178"/>
+      <c r="K144" s="178"/>
+      <c r="L144" s="178"/>
+      <c r="M144" s="178"/>
+      <c r="N144" s="178"/>
+      <c r="O144" s="178"/>
       <c r="P144" s="3"/>
       <c r="Q144" s="3"/>
       <c r="R144" s="3"/>
@@ -9982,24 +9982,24 @@
       <c r="T144" s="3"/>
       <c r="U144" s="3"/>
     </row>
-    <row r="145" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
-      <c r="C145" s="177" t="s">
+      <c r="C145" s="178" t="s">
         <v>319</v>
       </c>
-      <c r="D145" s="177"/>
-      <c r="E145" s="177"/>
-      <c r="F145" s="177"/>
-      <c r="G145" s="177"/>
-      <c r="H145" s="177"/>
-      <c r="I145" s="177"/>
-      <c r="J145" s="177"/>
-      <c r="K145" s="177"/>
-      <c r="L145" s="177"/>
-      <c r="M145" s="177"/>
-      <c r="N145" s="177"/>
-      <c r="O145" s="177"/>
+      <c r="D145" s="178"/>
+      <c r="E145" s="178"/>
+      <c r="F145" s="178"/>
+      <c r="G145" s="178"/>
+      <c r="H145" s="178"/>
+      <c r="I145" s="178"/>
+      <c r="J145" s="178"/>
+      <c r="K145" s="178"/>
+      <c r="L145" s="178"/>
+      <c r="M145" s="178"/>
+      <c r="N145" s="178"/>
+      <c r="O145" s="178"/>
       <c r="P145" s="3"/>
       <c r="Q145" s="3"/>
       <c r="R145" s="3"/>
@@ -10007,24 +10007,24 @@
       <c r="T145" s="3"/>
       <c r="U145" s="3"/>
     </row>
-    <row r="146" spans="1:21" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
-      <c r="C146" s="177" t="s">
+      <c r="C146" s="178" t="s">
         <v>320</v>
       </c>
-      <c r="D146" s="177"/>
-      <c r="E146" s="177"/>
-      <c r="F146" s="177"/>
-      <c r="G146" s="177"/>
-      <c r="H146" s="177"/>
-      <c r="I146" s="177"/>
-      <c r="J146" s="177"/>
-      <c r="K146" s="177"/>
-      <c r="L146" s="177"/>
-      <c r="M146" s="177"/>
-      <c r="N146" s="177"/>
-      <c r="O146" s="177"/>
+      <c r="D146" s="178"/>
+      <c r="E146" s="178"/>
+      <c r="F146" s="178"/>
+      <c r="G146" s="178"/>
+      <c r="H146" s="178"/>
+      <c r="I146" s="178"/>
+      <c r="J146" s="178"/>
+      <c r="K146" s="178"/>
+      <c r="L146" s="178"/>
+      <c r="M146" s="178"/>
+      <c r="N146" s="178"/>
+      <c r="O146" s="178"/>
       <c r="P146" s="3"/>
       <c r="Q146" s="4"/>
       <c r="R146" s="3"/>
@@ -10032,24 +10032,24 @@
       <c r="T146" s="3"/>
       <c r="U146" s="3"/>
     </row>
-    <row r="147" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
-      <c r="C147" s="177" t="s">
+      <c r="C147" s="178" t="s">
         <v>321</v>
       </c>
-      <c r="D147" s="177"/>
-      <c r="E147" s="177"/>
-      <c r="F147" s="177"/>
-      <c r="G147" s="177"/>
-      <c r="H147" s="177"/>
-      <c r="I147" s="177"/>
-      <c r="J147" s="177"/>
-      <c r="K147" s="177"/>
-      <c r="L147" s="177"/>
-      <c r="M147" s="177"/>
-      <c r="N147" s="177"/>
-      <c r="O147" s="177"/>
+      <c r="D147" s="178"/>
+      <c r="E147" s="178"/>
+      <c r="F147" s="178"/>
+      <c r="G147" s="178"/>
+      <c r="H147" s="178"/>
+      <c r="I147" s="178"/>
+      <c r="J147" s="178"/>
+      <c r="K147" s="178"/>
+      <c r="L147" s="178"/>
+      <c r="M147" s="178"/>
+      <c r="N147" s="178"/>
+      <c r="O147" s="178"/>
       <c r="P147" s="3"/>
       <c r="Q147" s="4"/>
       <c r="R147" s="3"/>
@@ -10057,24 +10057,24 @@
       <c r="T147" s="3"/>
       <c r="U147" s="3"/>
     </row>
-    <row r="148" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
-      <c r="C148" s="177" t="s">
+      <c r="C148" s="178" t="s">
         <v>322</v>
       </c>
-      <c r="D148" s="177"/>
-      <c r="E148" s="177"/>
-      <c r="F148" s="177"/>
-      <c r="G148" s="177"/>
-      <c r="H148" s="177"/>
-      <c r="I148" s="177"/>
-      <c r="J148" s="177"/>
-      <c r="K148" s="177"/>
-      <c r="L148" s="177"/>
-      <c r="M148" s="177"/>
-      <c r="N148" s="177"/>
-      <c r="O148" s="177"/>
+      <c r="D148" s="178"/>
+      <c r="E148" s="178"/>
+      <c r="F148" s="178"/>
+      <c r="G148" s="178"/>
+      <c r="H148" s="178"/>
+      <c r="I148" s="178"/>
+      <c r="J148" s="178"/>
+      <c r="K148" s="178"/>
+      <c r="L148" s="178"/>
+      <c r="M148" s="178"/>
+      <c r="N148" s="178"/>
+      <c r="O148" s="178"/>
       <c r="P148" s="4"/>
       <c r="Q148" s="4"/>
       <c r="R148" s="3"/>
@@ -10082,24 +10082,24 @@
       <c r="T148" s="3"/>
       <c r="U148" s="3"/>
     </row>
-    <row r="149" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
-      <c r="C149" s="178" t="s">
+      <c r="C149" s="179" t="s">
         <v>323</v>
       </c>
-      <c r="D149" s="178"/>
-      <c r="E149" s="178"/>
-      <c r="F149" s="178"/>
-      <c r="G149" s="178"/>
-      <c r="H149" s="178"/>
-      <c r="I149" s="178"/>
-      <c r="J149" s="178"/>
-      <c r="K149" s="178"/>
-      <c r="L149" s="178"/>
-      <c r="M149" s="178"/>
-      <c r="N149" s="178"/>
-      <c r="O149" s="178"/>
+      <c r="D149" s="179"/>
+      <c r="E149" s="179"/>
+      <c r="F149" s="179"/>
+      <c r="G149" s="179"/>
+      <c r="H149" s="179"/>
+      <c r="I149" s="179"/>
+      <c r="J149" s="179"/>
+      <c r="K149" s="179"/>
+      <c r="L149" s="179"/>
+      <c r="M149" s="179"/>
+      <c r="N149" s="179"/>
+      <c r="O149" s="179"/>
       <c r="P149" s="4"/>
       <c r="Q149" s="4"/>
       <c r="R149" s="3"/>
@@ -10107,7 +10107,7 @@
       <c r="T149" s="3"/>
       <c r="U149" s="3"/>
     </row>
-    <row r="150" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:21" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="175" t="s">
@@ -10132,7 +10132,7 @@
       <c r="T150" s="3"/>
       <c r="U150" s="3"/>
     </row>
-    <row r="151" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="D151" s="1"/>
@@ -10151,7 +10151,7 @@
       <c r="T151" s="3"/>
       <c r="U151" s="3"/>
     </row>
-    <row r="152" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P152" s="4"/>
       <c r="Q152" s="4"/>
       <c r="R152" s="3"/>
@@ -10159,7 +10159,7 @@
       <c r="T152" s="3"/>
       <c r="U152" s="3"/>
     </row>
-    <row r="153" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:21" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P153" s="4"/>
       <c r="Q153" s="4"/>
       <c r="R153" s="3"/>
@@ -10167,7 +10167,7 @@
       <c r="T153" s="3"/>
       <c r="U153" s="3"/>
     </row>
-    <row r="154" spans="1:21" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:21" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P154" s="4"/>
       <c r="Q154" s="4"/>
       <c r="R154" s="3"/>
@@ -10175,19 +10175,19 @@
       <c r="T154" s="3"/>
       <c r="U154" s="3"/>
     </row>
-    <row r="155" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P155" s="4"/>
       <c r="R155" s="3"/>
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
       <c r="U155" s="3"/>
     </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="P156" s="4"/>
       <c r="T156" s="3"/>
       <c r="U156" s="3"/>
     </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="T157" s="3"/>
       <c r="U157" s="3"/>
     </row>
@@ -10250,30 +10250,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O57"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="2" width="34.5546875" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="34.5703125" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="30.7109375" customWidth="1"/>
     <col min="5" max="5" width="14" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.88671875" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" customWidth="1"/>
-    <col min="9" max="9" width="24.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" customWidth="1"/>
+    <col min="8" max="8" width="22.28515625" customWidth="1"/>
+    <col min="9" max="9" width="24.5703125" style="2" customWidth="1"/>
     <col min="10" max="10" width="22" style="2" customWidth="1"/>
-    <col min="11" max="11" width="20.88671875" customWidth="1"/>
-    <col min="12" max="12" width="124.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="35.88671875" customWidth="1"/>
-    <col min="14" max="14" width="165.88671875" customWidth="1"/>
+    <col min="11" max="11" width="20.85546875" customWidth="1"/>
+    <col min="12" max="12" width="124.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="35.85546875" customWidth="1"/>
+    <col min="14" max="14" width="165.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="35" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>2</v>
       </c>
@@ -10314,7 +10314,7 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
         <v>335</v>
       </c>
@@ -10353,7 +10353,7 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="50" t="s">
         <v>335</v>
       </c>
@@ -10392,7 +10392,7 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="50" t="s">
         <v>342</v>
       </c>
@@ -10431,7 +10431,7 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="50" t="s">
         <v>346</v>
       </c>
@@ -10470,7 +10470,7 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="50" t="s">
         <v>342</v>
       </c>
@@ -10509,7 +10509,7 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="50" t="s">
         <v>342</v>
       </c>
@@ -10548,7 +10548,7 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="50" t="s">
         <v>342</v>
       </c>
@@ -10587,7 +10587,7 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="50" t="s">
         <v>356</v>
       </c>
@@ -10626,7 +10626,7 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="50" t="s">
         <v>360</v>
       </c>
@@ -10665,7 +10665,7 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="50" t="s">
         <v>363</v>
       </c>
@@ -10704,7 +10704,7 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="50" t="s">
         <v>363</v>
       </c>
@@ -10743,7 +10743,7 @@
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="50" t="s">
         <v>368</v>
       </c>
@@ -10782,7 +10782,7 @@
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="50" t="s">
         <v>368</v>
       </c>
@@ -10821,7 +10821,7 @@
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="50" t="s">
         <v>374</v>
       </c>
@@ -10860,7 +10860,7 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="50" t="s">
         <v>379</v>
       </c>
@@ -10899,220 +10899,218 @@
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="50" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E18" s="43">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="F18" s="31">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>238</v>
+        <v>32</v>
       </c>
       <c r="H18" s="43" t="s">
         <v>339</v>
       </c>
       <c r="I18" s="47">
-        <v>45596</v>
-      </c>
-      <c r="J18" s="45" t="s">
-        <v>340</v>
-      </c>
-      <c r="K18" s="45" t="s">
-        <v>340</v>
-      </c>
-      <c r="L18" s="46" t="s">
-        <v>385</v>
-      </c>
+        <v>45617</v>
+      </c>
+      <c r="J18" s="45">
+        <v>45663</v>
+      </c>
+      <c r="K18" s="45">
+        <v>45863</v>
+      </c>
+      <c r="L18" s="46"/>
       <c r="M18" s="12"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="50" t="s">
-        <v>363</v>
+        <v>388</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>387</v>
+        <v>41</v>
       </c>
       <c r="E19" s="43">
-        <v>22.8</v>
+        <v>100</v>
       </c>
       <c r="F19" s="31">
         <v>33</v>
       </c>
       <c r="G19" s="43" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H19" s="43" t="s">
         <v>339</v>
       </c>
       <c r="I19" s="47">
-        <v>45617</v>
+        <v>45635</v>
       </c>
       <c r="J19" s="45">
-        <v>45663</v>
+        <v>45673</v>
       </c>
       <c r="K19" s="45">
-        <v>45863</v>
+        <v>45808</v>
       </c>
       <c r="L19" s="46"/>
       <c r="M19" s="12"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="50" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C20" s="30" t="s">
         <v>40</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>41</v>
+        <v>348</v>
       </c>
       <c r="E20" s="43">
-        <v>100</v>
+        <v>17.16</v>
       </c>
       <c r="F20" s="31">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="G20" s="43" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H20" s="43" t="s">
-        <v>339</v>
-      </c>
-      <c r="I20" s="47">
-        <v>45635</v>
+        <v>349</v>
+      </c>
+      <c r="I20" s="36" t="s">
+        <v>340</v>
       </c>
       <c r="J20" s="45">
-        <v>45673</v>
+        <v>45799</v>
       </c>
       <c r="K20" s="45">
-        <v>45808</v>
+        <v>45824</v>
       </c>
       <c r="L20" s="46"/>
       <c r="M20" s="12"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="50" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>348</v>
+        <v>394</v>
       </c>
       <c r="E21" s="43">
-        <v>17.16</v>
+        <v>0</v>
       </c>
       <c r="F21" s="31">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="H21" s="43" t="s">
-        <v>349</v>
-      </c>
-      <c r="I21" s="36" t="s">
-        <v>340</v>
+        <v>339</v>
+      </c>
+      <c r="I21" s="47">
+        <v>45918</v>
       </c>
       <c r="J21" s="45">
-        <v>45799</v>
+        <v>45922</v>
       </c>
       <c r="K21" s="45">
-        <v>45824</v>
-      </c>
-      <c r="L21" s="46"/>
+        <v>45922</v>
+      </c>
+      <c r="L21" s="46" t="s">
+        <v>395</v>
+      </c>
       <c r="M21" s="12"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="50" t="s">
-        <v>392</v>
+        <v>356</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>394</v>
+        <v>358</v>
       </c>
       <c r="E22" s="43">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="F22" s="31">
-        <v>220</v>
+        <v>33</v>
       </c>
       <c r="G22" s="43" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="H22" s="43" t="s">
-        <v>339</v>
-      </c>
-      <c r="I22" s="47">
-        <v>45918</v>
+        <v>359</v>
+      </c>
+      <c r="I22" s="36" t="s">
+        <v>340</v>
       </c>
       <c r="J22" s="45">
-        <v>45922</v>
+        <v>45936</v>
       </c>
       <c r="K22" s="45">
-        <v>45922</v>
-      </c>
-      <c r="L22" s="46" t="s">
-        <v>395</v>
-      </c>
+        <v>46003</v>
+      </c>
+      <c r="L22" s="46"/>
       <c r="M22" s="12"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="50" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B23" s="44" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C23" s="30" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="30" t="s">
-        <v>358</v>
+        <v>398</v>
       </c>
       <c r="E23" s="43">
-        <v>22.4</v>
+        <v>23.75</v>
       </c>
       <c r="F23" s="31">
         <v>33</v>
@@ -11121,76 +11119,76 @@
         <v>32</v>
       </c>
       <c r="H23" s="43" t="s">
-        <v>359</v>
+        <v>399</v>
       </c>
       <c r="I23" s="36" t="s">
         <v>340</v>
       </c>
       <c r="J23" s="45">
-        <v>45936</v>
+        <v>45985</v>
       </c>
       <c r="K23" s="45">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="L23" s="46"/>
       <c r="M23" s="12"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="50" t="s">
-        <v>363</v>
+        <v>392</v>
       </c>
       <c r="B24" s="44" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E24" s="43">
-        <v>23.75</v>
+        <v>55</v>
       </c>
       <c r="F24" s="31">
-        <v>33</v>
+        <v>220</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="H24" s="43" t="s">
-        <v>399</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>340</v>
+        <v>339</v>
+      </c>
+      <c r="I24" s="47">
+        <v>45918</v>
       </c>
       <c r="J24" s="45">
-        <v>45985</v>
+        <v>45994</v>
       </c>
       <c r="K24" s="45">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="L24" s="46"/>
       <c r="M24" s="12"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
     </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="50" t="s">
-        <v>392</v>
+        <v>342</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="E25" s="43">
-        <v>55</v>
+        <v>56.87</v>
       </c>
       <c r="F25" s="31">
         <v>220</v>
@@ -11201,281 +11199,285 @@
       <c r="H25" s="43" t="s">
         <v>339</v>
       </c>
-      <c r="I25" s="47">
-        <v>45918</v>
+      <c r="I25" s="36" t="s">
+        <v>340</v>
       </c>
       <c r="J25" s="45">
-        <v>45994</v>
+        <v>46038</v>
       </c>
       <c r="K25" s="45">
-        <v>46014</v>
+        <v>46052</v>
       </c>
       <c r="L25" s="46"/>
       <c r="M25" s="12"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="50" t="s">
-        <v>342</v>
+        <v>403</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>402</v>
+        <v>348</v>
       </c>
       <c r="E26" s="43">
-        <v>56.87</v>
+        <v>24</v>
       </c>
       <c r="F26" s="31">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="H26" s="43" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="I26" s="36" t="s">
         <v>340</v>
       </c>
       <c r="J26" s="45">
-        <v>46038</v>
+        <v>46049</v>
       </c>
       <c r="K26" s="45">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="L26" s="46"/>
       <c r="M26" s="12"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="50" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="30" t="s">
-        <v>348</v>
-      </c>
-      <c r="E27" s="43">
-        <v>24</v>
-      </c>
-      <c r="F27" s="31">
-        <v>110</v>
+        <v>30</v>
+      </c>
+      <c r="D27" s="82" t="s">
+        <v>387</v>
+      </c>
+      <c r="E27" s="83">
+        <v>33</v>
+      </c>
+      <c r="F27" s="83">
+        <v>33</v>
       </c>
       <c r="G27" s="43" t="s">
         <v>32</v>
       </c>
       <c r="H27" s="43" t="s">
-        <v>349</v>
-      </c>
-      <c r="I27" s="36" t="s">
-        <v>340</v>
-      </c>
-      <c r="J27" s="45">
-        <v>46049</v>
-      </c>
-      <c r="K27" s="45">
-        <v>46064</v>
+        <v>339</v>
+      </c>
+      <c r="I27" s="76">
+        <v>45762</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>408</v>
+      </c>
+      <c r="K27" s="48" t="s">
+        <v>408</v>
       </c>
       <c r="L27" s="46"/>
       <c r="M27" s="12"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="50" t="s">
-        <v>390</v>
-      </c>
-      <c r="B28" s="44" t="s">
-        <v>405</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="82" t="s">
-        <v>366</v>
-      </c>
-      <c r="E28" s="83">
-        <v>27</v>
-      </c>
-      <c r="F28" s="83">
-        <v>33</v>
-      </c>
-      <c r="G28" s="43" t="s">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="127" t="s">
+        <v>409</v>
+      </c>
+      <c r="B28" s="128" t="s">
+        <v>410</v>
+      </c>
+      <c r="C28" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="129">
+        <v>150</v>
+      </c>
+      <c r="F28" s="129">
+        <v>110</v>
+      </c>
+      <c r="G28" s="130" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="43" t="s">
-        <v>367</v>
-      </c>
-      <c r="I28" s="76">
-        <v>45717</v>
-      </c>
-      <c r="J28" s="134">
-        <v>46160</v>
-      </c>
-      <c r="K28" s="134">
-        <v>46192</v>
+      <c r="H28" s="130" t="s">
+        <v>339</v>
+      </c>
+      <c r="I28" s="47">
+        <v>45825</v>
+      </c>
+      <c r="J28" s="47">
+        <v>46203</v>
+      </c>
+      <c r="K28" s="66">
+        <v>46254</v>
       </c>
       <c r="L28" s="46"/>
       <c r="M28" s="12"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
     </row>
-    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="50" t="s">
-        <v>406</v>
-      </c>
-      <c r="B29" s="44" t="s">
-        <v>407</v>
+    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>411</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="82" t="s">
-        <v>387</v>
-      </c>
-      <c r="E29" s="83">
-        <v>33</v>
-      </c>
-      <c r="F29" s="83">
-        <v>33</v>
-      </c>
-      <c r="G29" s="43" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>412</v>
+      </c>
+      <c r="E29" s="31">
+        <v>100</v>
+      </c>
+      <c r="F29" s="31">
+        <v>220</v>
+      </c>
+      <c r="G29" s="31" t="s">
+        <v>22</v>
       </c>
       <c r="H29" s="43" t="s">
         <v>339</v>
       </c>
-      <c r="I29" s="76">
-        <v>45762</v>
-      </c>
-      <c r="J29" s="49" t="s">
-        <v>408</v>
-      </c>
-      <c r="K29" s="48" t="s">
-        <v>408</v>
+      <c r="I29" s="47">
+        <v>45869</v>
+      </c>
+      <c r="J29" s="76">
+        <v>46209</v>
+      </c>
+      <c r="K29" s="60">
+        <v>46283</v>
       </c>
       <c r="L29" s="46"/>
       <c r="M29" s="12"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
     </row>
-    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="127" t="s">
-        <v>409</v>
-      </c>
-      <c r="B30" s="128" t="s">
-        <v>410</v>
-      </c>
-      <c r="C30" s="90" t="s">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="50" t="s">
+        <v>342</v>
+      </c>
+      <c r="B30" s="44" t="s">
+        <v>413</v>
+      </c>
+      <c r="C30" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="129">
-        <v>150</v>
-      </c>
-      <c r="F30" s="129">
+      <c r="D30" s="82" t="s">
+        <v>414</v>
+      </c>
+      <c r="E30" s="83">
+        <v>16</v>
+      </c>
+      <c r="F30" s="83">
         <v>110</v>
       </c>
-      <c r="G30" s="130" t="s">
-        <v>32</v>
-      </c>
-      <c r="H30" s="130" t="s">
+      <c r="G30" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="H30" s="43" t="s">
         <v>339</v>
       </c>
-      <c r="I30" s="47">
-        <v>45825</v>
-      </c>
-      <c r="J30" s="47">
-        <v>46203</v>
-      </c>
-      <c r="K30" s="66">
-        <v>46254</v>
-      </c>
-      <c r="L30" s="46"/>
+      <c r="I30" s="76">
+        <v>45901</v>
+      </c>
+      <c r="J30" s="49" t="s">
+        <v>340</v>
+      </c>
+      <c r="K30" s="48" t="s">
+        <v>340</v>
+      </c>
+      <c r="L30" s="46" t="s">
+        <v>415</v>
+      </c>
       <c r="M30" s="12"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
     </row>
-    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>411</v>
+    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="50" t="s">
+        <v>382</v>
+      </c>
+      <c r="B31" s="44" t="s">
+        <v>383</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>412</v>
-      </c>
-      <c r="E31" s="31">
-        <v>100</v>
+        <v>384</v>
+      </c>
+      <c r="E31" s="43">
+        <v>0</v>
       </c>
       <c r="F31" s="31">
-        <v>220</v>
-      </c>
-      <c r="G31" s="31" t="s">
-        <v>22</v>
+        <v>66</v>
+      </c>
+      <c r="G31" s="43" t="s">
+        <v>238</v>
       </c>
       <c r="H31" s="43" t="s">
         <v>339</v>
       </c>
       <c r="I31" s="47">
-        <v>45869</v>
-      </c>
-      <c r="J31" s="76">
-        <v>46209</v>
-      </c>
-      <c r="K31" s="60">
-        <v>46283</v>
-      </c>
-      <c r="L31" s="46"/>
+        <v>45909</v>
+      </c>
+      <c r="J31" s="45" t="s">
+        <v>340</v>
+      </c>
+      <c r="K31" s="45" t="s">
+        <v>340</v>
+      </c>
+      <c r="L31" s="46" t="s">
+        <v>385</v>
+      </c>
       <c r="M31" s="12"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="50" t="s">
-        <v>342</v>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="51" t="s">
+        <v>349</v>
       </c>
       <c r="B32" s="44" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="82" t="s">
-        <v>414</v>
+        <v>40</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>348</v>
       </c>
       <c r="E32" s="83">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F32" s="83">
         <v>110</v>
       </c>
       <c r="G32" s="43" t="s">
-        <v>238</v>
+        <v>417</v>
       </c>
       <c r="H32" s="43" t="s">
         <v>339</v>
       </c>
       <c r="I32" s="76">
-        <v>45901</v>
+        <v>46010</v>
       </c>
       <c r="J32" s="49" t="s">
         <v>340</v>
@@ -11484,54 +11486,52 @@
         <v>340</v>
       </c>
       <c r="L32" s="46" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M32" s="12"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="51" t="s">
-        <v>349</v>
+    <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="50" t="s">
+        <v>390</v>
       </c>
       <c r="B33" s="44" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>348</v>
+        <v>30</v>
+      </c>
+      <c r="D33" s="82" t="s">
+        <v>366</v>
       </c>
       <c r="E33" s="83">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="F33" s="83">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="G33" s="43" t="s">
-        <v>417</v>
+        <v>32</v>
       </c>
       <c r="H33" s="43" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="I33" s="76">
-        <v>46010</v>
-      </c>
-      <c r="J33" s="49" t="s">
-        <v>340</v>
-      </c>
-      <c r="K33" s="48" t="s">
-        <v>340</v>
-      </c>
-      <c r="L33" s="46" t="s">
-        <v>418</v>
-      </c>
+        <v>46112</v>
+      </c>
+      <c r="J33" s="134">
+        <v>46160</v>
+      </c>
+      <c r="K33" s="134">
+        <v>46192</v>
+      </c>
+      <c r="L33" s="46"/>
       <c r="M33" s="12"/>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="53" t="s">
         <v>356</v>
       </c>
@@ -11570,7 +11570,7 @@
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="53" t="s">
         <v>420</v>
       </c>
@@ -11609,7 +11609,7 @@
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="53" t="s">
         <v>422</v>
       </c>
@@ -11648,7 +11648,7 @@
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="53" t="s">
         <v>50</v>
       </c>
@@ -11687,7 +11687,7 @@
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="53" t="s">
         <v>427</v>
       </c>
@@ -11726,7 +11726,7 @@
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="53" t="s">
         <v>342</v>
       </c>
@@ -11765,7 +11765,7 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="53" t="s">
         <v>432</v>
       </c>
@@ -11804,7 +11804,7 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="53" t="s">
         <v>435</v>
       </c>
@@ -11843,7 +11843,7 @@
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="53" t="s">
         <v>450</v>
       </c>
@@ -11882,7 +11882,7 @@
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="53" t="s">
         <v>342</v>
       </c>
@@ -11921,7 +11921,7 @@
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="53" t="s">
         <v>363</v>
       </c>
@@ -11960,7 +11960,7 @@
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="33"/>
       <c r="B45" s="32"/>
       <c r="C45" s="33"/>
@@ -11970,16 +11970,16 @@
       <c r="G45" s="84"/>
       <c r="H45" s="84"/>
       <c r="I45" s="39"/>
-      <c r="J45" s="179" t="s">
+      <c r="J45" s="176" t="s">
         <v>437</v>
       </c>
-      <c r="K45" s="179"/>
+      <c r="K45" s="176"/>
       <c r="L45" s="3"/>
       <c r="M45" s="12"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
     </row>
-    <row r="46" spans="1:15" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A46" s="35" t="s">
         <v>438</v>
       </c>
@@ -11998,7 +11998,7 @@
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
     </row>
-    <row r="47" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
         <v>2</v>
       </c>
@@ -12039,7 +12039,7 @@
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="43" t="s">
         <v>443</v>
       </c>
@@ -12078,7 +12078,7 @@
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="43" t="s">
         <v>443</v>
       </c>
@@ -12117,7 +12117,7 @@
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="43" t="s">
         <v>443</v>
       </c>
@@ -12156,7 +12156,7 @@
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="33"/>
       <c r="B51" s="33"/>
       <c r="C51" s="33"/>
@@ -12173,7 +12173,7 @@
       <c r="N51" s="3"/>
       <c r="O51" s="3"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="33"/>
       <c r="B52" s="33"/>
       <c r="C52" s="33"/>
@@ -12190,7 +12190,7 @@
       <c r="N52" s="3"/>
       <c r="O52" s="3"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="33"/>
       <c r="B53" s="33"/>
       <c r="C53" s="33"/>
@@ -12207,7 +12207,7 @@
       <c r="N53" s="3"/>
       <c r="O53" s="3"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="33"/>
       <c r="B54" s="33"/>
       <c r="C54" s="33"/>
@@ -12224,7 +12224,7 @@
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -12239,7 +12239,7 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="175"/>
       <c r="B56" s="175"/>
       <c r="C56" s="175"/>
@@ -12254,7 +12254,7 @@
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -12270,22 +12270,22 @@
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="A45 G45 G51:G54 A50:A54" name="editablecellsgen_1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
     <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="E45:F45 H51:H54 E51:F54 H40:H45" name="editablecellsgen_6" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="21SrT9FQe05ypOyBw/ezVB+O6KVQBfmkSo/0DZXpJLpEl93HkzpfJzCZ3DrSbd3++L6bSblgczu/uV15PCPyBw==" saltValue="A+Im1Gl+izjKv1om6cfuug==" spinCount="100000" sqref="I51:J54 J28:J33 J50 I45:J45 I40:J44" name="editcellsnongen_3" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="21SrT9FQe05ypOyBw/ezVB+O6KVQBfmkSo/0DZXpJLpEl93HkzpfJzCZ3DrSbd3++L6bSblgczu/uV15PCPyBw==" saltValue="A+Im1Gl+izjKv1om6cfuug==" spinCount="100000" sqref="I51:J54 I40:J44 J50 I45:J45 J33 J27:J30 J32" name="editcellsnongen_3" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
     <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="G40:G44 A40:A44" name="editablecellsgen_1_2" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
     <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="E40:F44" name="editablecellsgen_6_1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
     <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="G47" name="editablecellsgen_1_3" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
     <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="H47 E47:F47" name="editablecellsgen_6_2" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
     <protectedRange algorithmName="SHA-512" hashValue="21SrT9FQe05ypOyBw/ezVB+O6KVQBfmkSo/0DZXpJLpEl93HkzpfJzCZ3DrSbd3++L6bSblgczu/uV15PCPyBw==" saltValue="A+Im1Gl+izjKv1om6cfuug==" spinCount="100000" sqref="I47" name="editcellsnongen_3_1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="G3:G27" name="editablecellsgen_1_5" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="E3:F27 H3:H27" name="editablecellsgen_6_4" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="21SrT9FQe05ypOyBw/ezVB+O6KVQBfmkSo/0DZXpJLpEl93HkzpfJzCZ3DrSbd3++L6bSblgczu/uV15PCPyBw==" saltValue="A+Im1Gl+izjKv1om6cfuug==" spinCount="100000" sqref="I3:J27" name="editcellsnongen_3_3" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="A3:A27" name="editablecellsgen_1_1_1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="G28:G30 G32:G33" name="editablecellsgen_1_6" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="E32:F33 E28:F30 H28:H33" name="editablecellsgen_6_5" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="21SrT9FQe05ypOyBw/ezVB+O6KVQBfmkSo/0DZXpJLpEl93HkzpfJzCZ3DrSbd3++L6bSblgczu/uV15PCPyBw==" saltValue="A+Im1Gl+izjKv1om6cfuug==" spinCount="100000" sqref="I28:I33" name="editcellsnongen_3_4" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="A28:A30 A32:A33" name="editablecellsgen_1_1_2" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="G31 A31" name="editablecellsgen_1_2_1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
-    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="E31:F31" name="editablecellsgen_6_1_1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="G18:G26 G3:G17 G31" name="editablecellsgen_1_5" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="H31 E18:F26 H3:H17 H18:H26 E3:F17 E31:F31" name="editablecellsgen_6_4" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="21SrT9FQe05ypOyBw/ezVB+O6KVQBfmkSo/0DZXpJLpEl93HkzpfJzCZ3DrSbd3++L6bSblgczu/uV15PCPyBw==" saltValue="A+Im1Gl+izjKv1om6cfuug==" spinCount="100000" sqref="I18:J26 I3:J17 I31:J31" name="editcellsnongen_3_3" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="A18:A26 A3:A17 A31" name="editablecellsgen_1_1_1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="G33 G27:G28 G30 G32" name="editablecellsgen_1_6" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="H33 E33:F33 H32 E27:F28 H27:H30 E30:F30 E32:F32" name="editablecellsgen_6_5" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="21SrT9FQe05ypOyBw/ezVB+O6KVQBfmkSo/0DZXpJLpEl93HkzpfJzCZ3DrSbd3++L6bSblgczu/uV15PCPyBw==" saltValue="A+Im1Gl+izjKv1om6cfuug==" spinCount="100000" sqref="I33 I27:I30 I32" name="editcellsnongen_3_4" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="A33 A27:A28 A30 A32" name="editablecellsgen_1_1_2" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="G29 A29" name="editablecellsgen_1_2_1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="E29:F29" name="editablecellsgen_6_1_1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
     <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="H34:H36 H38" name="editablecellsgen_6_6" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
     <protectedRange algorithmName="SHA-512" hashValue="21SrT9FQe05ypOyBw/ezVB+O6KVQBfmkSo/0DZXpJLpEl93HkzpfJzCZ3DrSbd3++L6bSblgczu/uV15PCPyBw==" saltValue="A+Im1Gl+izjKv1om6cfuug==" spinCount="100000" sqref="I34:J36 I38:J38" name="editcellsnongen_3_5" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
     <protectedRange algorithmName="SHA-512" hashValue="ro2lI7mCZ6MobNQYnP8+UfT6wgo2/FHeHzLIkZoqi2iljDqe3QAxYHlF9D74Y1bhJi6VUeQqtkrFuRVFHtQJoA==" saltValue="wp0USf4yXrqTzgkpEjjgyw==" spinCount="100000" sqref="A34:A39 G34:G36 G38" name="editablecellsgen_1_2_2" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-85022)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90025)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-88382)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-89301)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-25414)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-90113)(A;;CC;;;S-1-5-21-2002143706-767567037-1062434389-77158)"/>
@@ -12313,6 +12313,40 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="a6eebd71-b381-4cd7-b205-ff3a307ec7ec">CM010-1671997749-307</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="a6eebd71-b381-4cd7-b205-ff3a307ec7ec">
+      <Url>https://transpowernz.sharepoint.com/sites/cm010/_layouts/15/DocIdRedir.aspx?ID=CM010-1671997749-307</Url>
+      <Description>CM010-1671997749-307</Description>
+    </_dlc_DocIdUrl>
+    <SharedWithUsers xmlns="fd09b04b-c448-408d-b1d4-c0058ac8627f">
+      <UserInfo>
+        <DisplayName>Vanessa Head</DisplayName>
+        <AccountId>45</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Unmesh Vanka</DisplayName>
+        <AccountId>107</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="81773290-d8cd-4843-8446-d19dff1d7450" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -12360,40 +12394,6 @@
     <Filter/>
   </Receiver>
 </spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="a6eebd71-b381-4cd7-b205-ff3a307ec7ec">CM010-1671997749-307</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="a6eebd71-b381-4cd7-b205-ff3a307ec7ec">
-      <Url>https://transpowernz.sharepoint.com/sites/cm010/_layouts/15/DocIdRedir.aspx?ID=CM010-1671997749-307</Url>
-      <Description>CM010-1671997749-307</Description>
-    </_dlc_DocIdUrl>
-    <SharedWithUsers xmlns="fd09b04b-c448-408d-b1d4-c0058ac8627f">
-      <UserInfo>
-        <DisplayName>Vanessa Head</DisplayName>
-        <AccountId>45</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Unmesh Vanka</DisplayName>
-        <AccountId>107</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="81773290-d8cd-4843-8446-d19dff1d7450" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12610,9 +12610,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDE22E3E-F003-43F4-A75B-99C1DF0BD1F9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC49BD3B-3781-4860-B266-731C2C26B655}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12620,25 +12620,25 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57AC8DDD-8B23-4379-A799-87A0351AE492}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="fd09b04b-c448-408d-b1d4-c0058ac8627f"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="a6eebd71-b381-4cd7-b205-ff3a307ec7ec"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fd09b04b-c448-408d-b1d4-c0058ac8627f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a6eebd71-b381-4cd7-b205-ff3a307ec7ec"/>
     <ds:schemaRef ds:uri="81773290-d8cd-4843-8446-d19dff1d7450"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC49BD3B-3781-4860-B266-731C2C26B655}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDE22E3E-F003-43F4-A75B-99C1DF0BD1F9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
